--- a/PRODUCTION SUPPLIERS.xlsx
+++ b/PRODUCTION SUPPLIERS.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CristianSima\Desktop\Training\FUNDAMENTALS\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D6B0508-9610-4533-B3C3-A54102E71976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AABD1CE-BF7C-48DA-A98A-ADFD36220AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1AA4EA5-F547-467A-BE0C-166DAD2E52FC}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="PRODUCTION SUPPLIERS" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
